--- a/new-stats/sc-cambuur.xlsx
+++ b/new-stats/sc-cambuur.xlsx
@@ -569,22 +569,62 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>15/08/2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sittard</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>3</v>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Cambuur</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="M3" t="n">
+        <v>19</v>
+      </c>
+      <c r="N3" t="n">
+        <v>17</v>
+      </c>
+      <c r="O3" t="n">
+        <v>7</v>
+      </c>
+      <c r="P3" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr"/>
